--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_10-07-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_10-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Mannok_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7D2641-86A4-4CD6-87A0-F45F7FAFE872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FB024F-7C0A-4794-92F5-F843E6884432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="1500" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33060" yWindow="2445" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="71">
   <si>
     <t>SKU</t>
   </si>
@@ -193,31 +193,46 @@
     <t>£59.75</t>
   </si>
   <si>
-    <t>£15.44</t>
-  </si>
-  <si>
-    <t>£23.42</t>
-  </si>
-  <si>
-    <t>£30.08</t>
-  </si>
-  <si>
-    <t>£33.02</t>
-  </si>
-  <si>
-    <t>£36.74</t>
-  </si>
-  <si>
-    <t>£40.42</t>
-  </si>
-  <si>
-    <t>£39.91</t>
-  </si>
-  <si>
-    <t>£49.61</t>
-  </si>
-  <si>
-    <t>£59.79</t>
+    <t>£15.39</t>
+  </si>
+  <si>
+    <t>£18.05</t>
+  </si>
+  <si>
+    <t>£22.33</t>
+  </si>
+  <si>
+    <t>£23.36</t>
+  </si>
+  <si>
+    <t>£29.89</t>
+  </si>
+  <si>
+    <t>£32.94</t>
+  </si>
+  <si>
+    <t>£36.65</t>
+  </si>
+  <si>
+    <t>£40.32</t>
+  </si>
+  <si>
+    <t>£39.84</t>
+  </si>
+  <si>
+    <t>£49.09</t>
+  </si>
+  <si>
+    <t>£49.49</t>
+  </si>
+  <si>
+    <t>£59.54</t>
+  </si>
+  <si>
+    <t>£60.08</t>
+  </si>
+  <si>
+    <t>£59.64</t>
   </si>
 </sst>
 </file>
@@ -652,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -678,7 +693,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -704,7 +719,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -730,7 +745,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -756,7 +771,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -782,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -808,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -834,7 +849,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -860,7 +875,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -886,7 +901,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -912,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -964,7 +979,7 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -990,7 +1005,7 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1016,7 +1031,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
